--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F638411B-4371-42BE-B09F-B5321BA58043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9892CFE-140A-4526-9032-00EFB3971EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -518,9 +518,6 @@
     <t>Tính thuế thử việc</t>
   </si>
   <si>
-    <t>Tăng ca miễn thuế</t>
-  </si>
-  <si>
     <t>Tổng thu nhập</t>
   </si>
   <si>
@@ -549,6 +546,10 @@
   </si>
   <si>
     <t>Truy thu BH</t>
+  </si>
+  <si>
+    <t>Tiền lương ngày thực trả
+Actual wage per day</t>
   </si>
 </sst>
 </file>
@@ -1102,26 +1103,50 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1129,43 +1154,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="12" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1174,56 +1175,58 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma 2 2 2" xfId="2" xr:uid="{F56B0337-0F8B-4943-BF83-EA71CD031E4E}"/>
@@ -1629,7 +1632,9 @@
     <col min="49" max="50" width="9.140625" style="4"/>
     <col min="51" max="51" width="26.5703125" style="4" customWidth="1"/>
     <col min="52" max="52" width="23.28515625" style="4" customWidth="1"/>
-    <col min="53" max="16384" width="9.140625" style="4"/>
+    <col min="53" max="59" width="9.140625" style="4"/>
+    <col min="60" max="60" width="12.5703125" style="4" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1637,20 +1642,9 @@
         <v>1</v>
       </c>
       <c r="O1" s="4"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="96"/>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
-      <c r="AG1" s="96"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="59"/>
+      <c r="AE1" s="4"/>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
@@ -1664,29 +1658,18 @@
       <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="K2" s="86" t="s">
+      <c r="K2" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="86"/>
+      <c r="L2" s="65"/>
       <c r="M2" s="54">
         <f>BO14</f>
         <v>0</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="96"/>
-      <c r="X2" s="96"/>
-      <c r="Y2" s="96"/>
-      <c r="Z2" s="96"/>
-      <c r="AA2" s="96"/>
-      <c r="AB2" s="96"/>
-      <c r="AC2" s="96"/>
-      <c r="AD2" s="96"/>
-      <c r="AE2" s="96"/>
-      <c r="AF2" s="96"/>
-      <c r="AG2" s="96"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="59"/>
+      <c r="AE2" s="4"/>
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
@@ -1701,20 +1684,9 @@
         <v>3</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="96"/>
-      <c r="AD3" s="96"/>
-      <c r="AE3" s="96"/>
-      <c r="AF3" s="96"/>
-      <c r="AG3" s="96"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="59"/>
+      <c r="AE3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
@@ -1729,20 +1701,9 @@
         <v>4</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="96"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="96"/>
-      <c r="X4" s="96"/>
-      <c r="Y4" s="96"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="96"/>
-      <c r="AC4" s="96"/>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="96"/>
-      <c r="AF4" s="96"/>
-      <c r="AG4" s="96"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="59"/>
+      <c r="AE4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
@@ -1757,20 +1718,9 @@
         <v>5</v>
       </c>
       <c r="O5" s="4"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="97"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="96"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="59"/>
+      <c r="AE5" s="4"/>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
@@ -1815,38 +1765,36 @@
         <v>54</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="T6" s="96"/>
-      <c r="U6" s="96"/>
-      <c r="V6" s="97" t="s">
+      <c r="U6" s="4"/>
+      <c r="V6" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="96" t="s">
+      <c r="W6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="X6" s="96" t="s">
+      <c r="X6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Y6" s="96" t="s">
+      <c r="Y6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Z6" s="96" t="s">
+      <c r="Z6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AA6" s="96" t="s">
+      <c r="AA6" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AB6" s="96" t="s">
+      <c r="AB6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AC6" s="98"/>
-      <c r="AD6" s="96" t="s">
+      <c r="AC6"/>
+      <c r="AD6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AE6" s="96" t="s">
+      <c r="AE6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AF6" s="96"/>
-      <c r="AG6" s="96" t="s">
+      <c r="AG6" s="4" t="s">
         <v>82</v>
       </c>
       <c r="AI6" s="4" t="s">
@@ -1885,15 +1833,15 @@
         <v>55</v>
       </c>
       <c r="BF6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="BG6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="BH6" s="4" t="s">
+      <c r="BI6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BK6" s="4" t="s">
+      <c r="BL6" s="4" t="s">
         <v>143</v>
       </c>
       <c r="BM6" s="4" t="s">
@@ -1906,7 +1854,7 @@
         <v>78</v>
       </c>
       <c r="BP6" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BQ6" s="4" t="s">
         <v>60</v>
@@ -1921,13 +1869,13 @@
         <v>70</v>
       </c>
       <c r="BU6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BV6" s="4" t="s">
         <v>76</v>
       </c>
       <c r="BW6" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BX6" s="4" t="s">
         <v>71</v>
@@ -1976,46 +1924,46 @@
       <c r="S7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T7" s="96" t="s">
+      <c r="T7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="96" t="s">
+      <c r="U7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V7" s="97" t="s">
+      <c r="V7" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="W7" s="96" t="s">
+      <c r="W7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="96" t="s">
+      <c r="X7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="Y7" s="96" t="s">
+      <c r="Y7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="Z7" s="96" t="s">
+      <c r="Z7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA7" s="96" t="s">
+      <c r="AA7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AB7" s="96" t="s">
+      <c r="AB7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="AC7" s="96" t="s">
+      <c r="AC7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AD7" s="96" t="s">
+      <c r="AD7" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AE7" s="96" t="s">
+      <c r="AE7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AF7" s="96" t="s">
+      <c r="AF7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AG7" s="96" t="s">
+      <c r="AG7" s="4" t="s">
         <v>121</v>
       </c>
       <c r="AH7" s="4" t="s">
@@ -2067,10 +2015,10 @@
         <v>55</v>
       </c>
       <c r="BF7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG7" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="BG7" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2081,30 +2029,19 @@
         <v>48</v>
       </c>
       <c r="O8" s="4"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="97"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="59"/>
+      <c r="AE8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AS8" s="4"/>
       <c r="BE8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="BF8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG8" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="BG8" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2162,46 +2099,46 @@
       <c r="S9" s="4">
         <v>1</v>
       </c>
-      <c r="T9" s="96">
-        <v>1</v>
-      </c>
-      <c r="U9" s="96">
-        <v>1</v>
-      </c>
-      <c r="V9" s="97">
-        <v>1</v>
-      </c>
-      <c r="W9" s="96">
-        <v>1</v>
-      </c>
-      <c r="X9" s="96">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="96">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="96">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="96">
+      <c r="T9" s="4">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4">
+        <v>1</v>
+      </c>
+      <c r="V9" s="59">
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>1</v>
+      </c>
+      <c r="X9" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="4">
         <v>1</v>
       </c>
       <c r="AH9" s="4">
@@ -2287,46 +2224,46 @@
       <c r="S10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T10" s="96" t="s">
+      <c r="T10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U10" s="96" t="s">
+      <c r="U10" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V10" s="97" t="s">
+      <c r="V10" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="W10" s="96" t="s">
+      <c r="W10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X10" s="96" t="s">
+      <c r="X10" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="Y10" s="96" t="s">
+      <c r="Y10" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="Z10" s="96" t="s">
+      <c r="Z10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA10" s="96" t="s">
+      <c r="AA10" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AB10" s="96" t="s">
+      <c r="AB10" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="AC10" s="96" t="s">
+      <c r="AC10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AD10" s="96" t="s">
+      <c r="AD10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AE10" s="96" t="s">
+      <c r="AE10" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AF10" s="96" t="s">
+      <c r="AF10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AG10" s="96" t="s">
+      <c r="AG10" s="4" t="s">
         <v>121</v>
       </c>
       <c r="AH10" s="4" t="s">
@@ -2376,25 +2313,25 @@
       </c>
     </row>
     <row r="11" spans="1:77" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="62" t="s">
+      <c r="B11" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="89" t="s">
+      <c r="G11" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="91" t="s">
+      <c r="H11" s="72" t="s">
         <v>5</v>
       </c>
       <c r="I11" s="61" t="s">
@@ -2408,14 +2345,14 @@
         <v>7</v>
       </c>
       <c r="O11" s="61"/>
-      <c r="P11" s="83" t="s">
+      <c r="P11" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="59" t="s">
+      <c r="Q11" s="63"/>
+      <c r="R11" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="S11" s="60"/>
+      <c r="S11" s="84"/>
       <c r="T11" s="61" t="s">
         <v>10</v>
       </c>
@@ -2432,39 +2369,39 @@
       <c r="AE11" s="61"/>
       <c r="AF11" s="61"/>
       <c r="AG11" s="61"/>
-      <c r="AH11" s="62" t="s">
+      <c r="AH11" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="AI11" s="70" t="s">
+      <c r="AI11" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="AJ11" s="70"/>
-      <c r="AK11" s="70"/>
-      <c r="AL11" s="70"/>
-      <c r="AM11" s="70"/>
-      <c r="AN11" s="70"/>
-      <c r="AO11" s="70"/>
-      <c r="AP11" s="71" t="s">
+      <c r="AJ11" s="89"/>
+      <c r="AK11" s="89"/>
+      <c r="AL11" s="89"/>
+      <c r="AM11" s="89"/>
+      <c r="AN11" s="89"/>
+      <c r="AO11" s="89"/>
+      <c r="AP11" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="AQ11" s="73" t="s">
+      <c r="AQ11" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="AR11" s="74"/>
-      <c r="AS11" s="74"/>
-      <c r="AT11" s="74"/>
-      <c r="AU11" s="74"/>
-      <c r="AV11" s="75" t="s">
+      <c r="AR11" s="93"/>
+      <c r="AS11" s="93"/>
+      <c r="AT11" s="93"/>
+      <c r="AU11" s="93"/>
+      <c r="AV11" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="AW11" s="77" t="s">
+      <c r="AW11" s="96" t="s">
         <v>16</v>
       </c>
       <c r="AX11" s="7"/>
-      <c r="AY11" s="64" t="s">
+      <c r="AY11" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AZ11" s="68" t="s">
+      <c r="AZ11" s="87" t="s">
         <v>18</v>
       </c>
       <c r="BA11" s="8"/>
@@ -2479,56 +2416,58 @@
       <c r="BG11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BH11" s="66" t="s">
+      <c r="BH11" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="BI11" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="BI11" s="66" t="s">
-        <v>149</v>
-      </c>
-      <c r="BJ11" s="93" t="s">
+      <c r="BJ11" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK11" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="BK11" s="94"/>
-      <c r="BL11" s="94"/>
-      <c r="BM11" s="95"/>
-      <c r="BN11" s="66" t="s">
+      <c r="BL11" s="77"/>
+      <c r="BM11" s="78"/>
+      <c r="BN11" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="BO11" s="80" t="s">
+      <c r="BO11" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="BP11" s="66" t="s">
-        <v>151</v>
+      <c r="BP11" s="74" t="s">
+        <v>150</v>
       </c>
       <c r="BQ11" s="82" t="s">
         <v>59</v>
       </c>
       <c r="BR11" s="82"/>
-      <c r="BS11" s="80" t="s">
+      <c r="BS11" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="BT11" s="80"/>
-      <c r="BU11" s="85" t="s">
-        <v>158</v>
+      <c r="BT11" s="79"/>
+      <c r="BU11" s="64" t="s">
+        <v>157</v>
       </c>
       <c r="BV11" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="BW11" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="BW11" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="BY11" s="79" t="s">
+      <c r="BY11" s="80" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:77" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="88"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="92"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="73"/>
       <c r="I12" s="48" t="s">
         <v>20</v>
       </c>
@@ -2601,10 +2540,10 @@
       <c r="AF12" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="AG12" s="99" t="s">
+      <c r="AG12" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="AH12" s="63"/>
+      <c r="AH12" s="69"/>
       <c r="AI12" s="49">
         <v>1.5</v>
       </c>
@@ -2626,7 +2565,7 @@
       <c r="AO12" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AP12" s="72"/>
+      <c r="AP12" s="91"/>
       <c r="AQ12" s="46" t="s">
         <v>42</v>
       </c>
@@ -2642,11 +2581,11 @@
       <c r="AU12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="AV12" s="76"/>
-      <c r="AW12" s="78"/>
+      <c r="AV12" s="95"/>
+      <c r="AW12" s="97"/>
       <c r="AX12" s="9"/>
-      <c r="AY12" s="65"/>
-      <c r="AZ12" s="69"/>
+      <c r="AY12" s="86"/>
+      <c r="AZ12" s="88"/>
       <c r="BA12" s="10" t="str">
         <f>+IF(C12="SK2","SK2",IF(C12="FACTORY A","SK1 Box",IF(C12="FACTORY D","SK1 Bag","Chia")))</f>
         <v>Chia</v>
@@ -2656,23 +2595,21 @@
         <f>+IF(BA12="SK1 Box","Box",IF(BA12="Seaman","Seaman","Bag"))</f>
         <v>Bag</v>
       </c>
-      <c r="BH12" s="67"/>
-      <c r="BI12" s="67"/>
-      <c r="BJ12" s="35" t="s">
+      <c r="BH12" s="99"/>
+      <c r="BI12" s="75"/>
+      <c r="BJ12" s="75"/>
+      <c r="BK12" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="BK12" s="35" t="s">
+      <c r="BL12" s="35" t="s">
         <v>92</v>
-      </c>
-      <c r="BL12" s="35" t="s">
-        <v>148</v>
       </c>
       <c r="BM12" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="BN12" s="67"/>
-      <c r="BO12" s="80"/>
-      <c r="BP12" s="67"/>
+      <c r="BN12" s="75"/>
+      <c r="BO12" s="79"/>
+      <c r="BP12" s="75"/>
       <c r="BQ12" s="34">
         <v>1</v>
       </c>
@@ -2685,13 +2622,13 @@
       <c r="BT12" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="BU12" s="85"/>
+      <c r="BU12" s="64"/>
       <c r="BV12" s="81"/>
-      <c r="BW12" s="79"/>
+      <c r="BW12" s="80"/>
       <c r="BX12" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BY12" s="79"/>
+      <c r="BY12" s="80"/>
     </row>
     <row r="13" spans="1:77" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
@@ -2765,59 +2702,59 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T13" s="100">
+      <c r="T13" s="44">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U13" s="100">
+      <c r="U13" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V13" s="100">
+      <c r="V13" s="44">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W13" s="100">
+      <c r="W13" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X13" s="100">
+      <c r="X13" s="44">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y13" s="100">
+      <c r="Y13" s="44">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z13" s="100">
+      <c r="Z13" s="44">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA13" s="100">
+      <c r="AA13" s="44">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB13" s="100">
+      <c r="AB13" s="44">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC13" s="100">
+      <c r="AC13" s="44">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD13" s="100">
+      <c r="AD13" s="44">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE13" s="100">
+      <c r="AE13" s="44">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF13" s="100">
+      <c r="AF13" s="44">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG13" s="100">
+      <c r="AG13" s="44">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -2939,9 +2876,9 @@
         <f>(BR14)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="23" t="e">
-        <f>ROUND((M14/IF($M$2&gt;26,26,BO14)/8*BR14)*0.3,0)</f>
-        <v>#DIV/0!</v>
+      <c r="S14" s="23">
+        <f>ROUND(BH14/8*BR14*0.3,0)</f>
+        <v>0</v>
       </c>
       <c r="T14" s="23" t="e">
         <f>O14+Q14+S14</f>
@@ -2982,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="AF14" s="23">
-        <f>IF(AND(BV14="Female",BQ14+BR14+BS14&gt;=13*8),1.5*M14/IF($M$2*8&gt;208,208,BO14*8),0)</f>
+        <f>IF(AND(BV14="Female",BQ14+BR14+BS14&gt;=13*8),1.5*BH14/8,0)</f>
         <v>0</v>
       </c>
       <c r="AG14" s="30">
@@ -3010,9 +2947,9 @@
       <c r="AN14" s="24">
         <v>0</v>
       </c>
-      <c r="AO14" s="50" t="e">
-        <f>ROUND(M14/IF($M$2*8&gt;208,208,BO14*8)*(AI14*1.5  + AJ14* 2  + AK14* 2.1  + AL14* 2.7  + AM14* 3 + AN14* 3.9),0)</f>
-        <v>#DIV/0!</v>
+      <c r="AO14" s="50">
+        <f>ROUND(BH14/8*(AI14*1.5  + AJ14* 2  + AK14* 2.1  + AL14* 2.7  + AM14* 3 + AN14* 3.9),0)</f>
+        <v>0</v>
       </c>
       <c r="AP14" s="31" t="e">
         <f>ROUND(AH14+AO14,0)</f>
@@ -3027,7 +2964,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AS14" s="51" t="e">
-        <f>IF(BM14=1,IF(BI14&gt;11000000,BI14*10%,0),IF(BJ14&gt;0,ROUND(IF(BJ14&lt;5000000,BJ14*0.05,IF(BJ14&lt;10000000,BJ14*0.1-250000,IF(BJ14&lt;18000000,BJ14*0.15-750000,IF(BJ14&lt;32000000,BJ14*0.2-1650000,IF(BJ14&lt;52000000,BJ14*0.25-3250000,IF(BJ14&lt;80000000,BJ14*0.3-5850000,BJ14*0.35-9850000)))))),0),0))</f>
+        <f>IF(BM14=1,IF(BJ14&gt;11000000,BJ14*10%,0),IF(BK14&gt;0,ROUND(IF(BK14&lt;5000000,BK14*0.05,IF(BK14&lt;10000000,BK14*0.1-250000,IF(BK14&lt;18000000,BK14*0.15-750000,IF(BK14&lt;32000000,BK14*0.2-1650000,IF(BK14&lt;52000000,BK14*0.25-3250000,IF(BK14&lt;80000000,BK14*0.3-5850000,BK14*0.35-9850000)))))),0),0))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT14" s="23">
@@ -3070,22 +3007,22 @@
         <v>5</v>
       </c>
       <c r="BH14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="37" t="e">
+        <f>IF(N14&gt;0,O14/IF(N14&gt;26,26,N14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="37" t="e">
         <f>AP14 + BN14 - AQ14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BJ14" s="4" t="e">
-        <f>BI14 - BL14 - U14 - BK14*4400000 - 11000000</f>
+      <c r="BK14" s="100" t="e">
+        <f>BJ14 -#REF! - U14 - BL14*4400000 - 11000000 - ROUND(BH14/8*(BR14*0.3 + AI14*0.5 + AJ14* 1 + AK14* 1.1 + AL14* 1.7 + AM14* 2 + AN14* 2.9),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BK14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL14" s="38" t="e">
-        <f>ROUND(M14/IF($M$2*8&gt;208,208,BO14*8)*(BR14*0.3 + AI14*0.5 + AJ14* 1 + AK14* 1.1 + AL14* 1.7 + AM14* 2 + AN14* 2.9),0)</f>
-        <v>#DIV/0!</v>
+      <c r="BL14" s="4">
+        <v>0</v>
       </c>
       <c r="BM14" s="38"/>
       <c r="BN14" s="38">
@@ -3124,7 +3061,25 @@
     </row>
   </sheetData>
   <autoFilter ref="A13:BC13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="33">
+  <mergeCells count="34">
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:AG11"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AY11:AY12"/>
+    <mergeCell ref="BN11:BN12"/>
+    <mergeCell ref="AZ11:AZ12"/>
+    <mergeCell ref="BI11:BI12"/>
+    <mergeCell ref="AI11:AO11"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AU11"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="BH11:BH12"/>
+    <mergeCell ref="BY11:BY12"/>
+    <mergeCell ref="BS11:BT11"/>
+    <mergeCell ref="BW11:BW12"/>
+    <mergeCell ref="BV11:BV12"/>
+    <mergeCell ref="BQ11:BR11"/>
     <mergeCell ref="N11:O11"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="BU11:BU12"/>
@@ -3138,26 +3093,9 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:M11"/>
     <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BJ11:BM11"/>
-    <mergeCell ref="BI11:BI12"/>
+    <mergeCell ref="BK11:BM11"/>
+    <mergeCell ref="BJ11:BJ12"/>
     <mergeCell ref="BO11:BO12"/>
-    <mergeCell ref="BY11:BY12"/>
-    <mergeCell ref="BS11:BT11"/>
-    <mergeCell ref="BW11:BW12"/>
-    <mergeCell ref="BV11:BV12"/>
-    <mergeCell ref="BQ11:BR11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:AG11"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="AY11:AY12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="AZ11:AZ12"/>
-    <mergeCell ref="BH11:BH12"/>
-    <mergeCell ref="AI11:AO11"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AU11"/>
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AW11:AW12"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C11:C13 D13:AW13">

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9892CFE-140A-4526-9032-00EFB3971EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A46BDD-EA03-4448-AF8D-2BDF622C6FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$13:$BC$13</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
   <si>
     <t>TT
 No.</t>
@@ -550,6 +561,54 @@
   <si>
     <t>Tiền lương ngày thực trả
 Actual wage per day</t>
+  </si>
+  <si>
+    <t>s43</t>
+  </si>
+  <si>
+    <t>s46</t>
+  </si>
+  <si>
+    <t>s47</t>
+  </si>
+  <si>
+    <t>s48</t>
+  </si>
+  <si>
+    <t>s49</t>
+  </si>
+  <si>
+    <t>s50</t>
+  </si>
+  <si>
+    <t>s51</t>
+  </si>
+  <si>
+    <t>s52</t>
+  </si>
+  <si>
+    <t>s53</t>
+  </si>
+  <si>
+    <t>s54</t>
+  </si>
+  <si>
+    <t>s55</t>
+  </si>
+  <si>
+    <t>s57</t>
+  </si>
+  <si>
+    <t>s58</t>
+  </si>
+  <si>
+    <t>s59</t>
+  </si>
+  <si>
+    <t>PITDiff</t>
+  </si>
+  <si>
+    <t>PIT</t>
   </si>
 </sst>
 </file>
@@ -661,7 +720,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -929,6 +988,17 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -939,7 +1009,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1109,6 +1179,84 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1124,48 +1272,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1175,39 +1281,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1226,7 +1299,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma 2 2 2" xfId="2" xr:uid="{F56B0337-0F8B-4943-BF83-EA71CD031E4E}"/>
@@ -1292,7 +1373,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>515470</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>238993</xdr:rowOff>
+      <xdr:rowOff>245343</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1591,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY14"/>
+  <dimension ref="A1:BZ14"/>
   <sheetFormatPr defaultRowHeight="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0" style="4" hidden="1" customWidth="1"/>
@@ -1605,18 +1686,17 @@
     <col min="9" max="10" width="13.28515625" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" style="4" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9" style="4" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" style="38" customWidth="1"/>
-    <col min="16" max="16" width="9" style="4" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4" customWidth="1"/>
-    <col min="19" max="20" width="13.28515625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="38" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" style="56" customWidth="1"/>
-    <col min="23" max="24" width="10.7109375" style="4" customWidth="1"/>
-    <col min="25" max="25" width="15" style="4" customWidth="1"/>
-    <col min="26" max="30" width="10.7109375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="9" style="4" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="38" customWidth="1"/>
+    <col min="17" max="17" width="9" style="4" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" style="4" customWidth="1"/>
+    <col min="19" max="19" width="9" style="4" customWidth="1"/>
+    <col min="20" max="21" width="13.28515625" style="4" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="38" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" style="56" customWidth="1"/>
+    <col min="24" max="30" width="10.7109375" style="4" customWidth="1"/>
     <col min="31" max="31" width="13" style="38" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" style="4" customWidth="1"/>
     <col min="33" max="33" width="10.85546875" style="4" customWidth="1"/>
@@ -1634,16 +1714,19 @@
     <col min="52" max="52" width="23.28515625" style="4" customWidth="1"/>
     <col min="53" max="59" width="9.140625" style="4"/>
     <col min="60" max="60" width="12.5703125" style="4" customWidth="1"/>
-    <col min="61" max="16384" width="9.140625" style="4"/>
+    <col min="61" max="61" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="62" max="64" width="9.140625" style="4"/>
+    <col min="65" max="65" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="66" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:78" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4">
         <v>1</v>
       </c>
-      <c r="O1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="59"/>
+      <c r="P1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="59"/>
       <c r="AE1" s="4"/>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
@@ -1654,21 +1737,21 @@
       <c r="AQ1" s="4"/>
       <c r="AS1" s="4"/>
     </row>
-    <row r="2" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:78" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="65"/>
-      <c r="M2" s="54">
+      <c r="L2" s="91"/>
+      <c r="N2" s="54">
         <f>BO14</f>
         <v>0</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="59"/>
+      <c r="P2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="59"/>
       <c r="AE2" s="4"/>
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
@@ -1679,13 +1762,13 @@
       <c r="AQ2" s="4"/>
       <c r="AS2" s="4"/>
     </row>
-    <row r="3" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:78" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3</v>
       </c>
-      <c r="O3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="59"/>
+      <c r="P3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="59"/>
       <c r="AE3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
@@ -1696,13 +1779,13 @@
       <c r="AQ3" s="4"/>
       <c r="AS3" s="4"/>
     </row>
-    <row r="4" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:78" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>4</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="59"/>
+      <c r="P4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="59"/>
       <c r="AE4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
@@ -1713,24 +1796,163 @@
       <c r="AQ4" s="4"/>
       <c r="AS4" s="4"/>
     </row>
-    <row r="5" spans="1:77" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:78" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>5</v>
       </c>
-      <c r="O5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="59"/>
-      <c r="AE5" s="4"/>
-      <c r="AI5" s="4"/>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="4"/>
-      <c r="AL5" s="4"/>
-      <c r="AM5" s="4"/>
-      <c r="AN5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="AQ5" s="4"/>
       <c r="AS5" s="4"/>
+      <c r="AT5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BI5" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="BL5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="BM5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="BN5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="BP5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="BQ5" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="BR5" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="BS5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="BT5" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="BU5" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="BV5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="BW5" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="BX5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="BY5" s="4" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="6" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:78" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>6</v>
       </c>
@@ -1764,19 +1986,19 @@
       <c r="L6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="59" t="s">
+      <c r="M6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="X6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="Y6" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="Z6" s="4" t="s">
         <v>83</v>
@@ -1883,8 +2105,11 @@
       <c r="BY6" s="4" t="s">
         <v>89</v>
       </c>
+      <c r="BZ6" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
-    <row r="7" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:78" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>7</v>
       </c>
@@ -1904,43 +2129,43 @@
         <v>100</v>
       </c>
       <c r="M7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="R7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="S7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="T7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V7" s="59" t="s">
+      <c r="W7" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="X7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="Y7" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="Z7" s="4" t="s">
         <v>114</v>
@@ -2021,16 +2246,16 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:78" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="59"/>
+      <c r="P8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="59"/>
       <c r="AE8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AS8" s="4"/>
@@ -2044,7 +2269,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:77" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:78" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>9</v>
       </c>
@@ -2105,10 +2330,10 @@
       <c r="U9" s="4">
         <v>1</v>
       </c>
-      <c r="V9" s="59">
-        <v>1</v>
-      </c>
-      <c r="W9" s="4">
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
+      <c r="W9" s="59">
         <v>1</v>
       </c>
       <c r="X9" s="4">
@@ -2187,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:77" ht="25.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:78" ht="25.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>10</v>
       </c>
@@ -2204,43 +2429,43 @@
         <v>100</v>
       </c>
       <c r="M10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="T10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V10" s="59" t="s">
+      <c r="W10" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="X10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="Y10" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="Z10" s="4" t="s">
         <v>114</v>
@@ -2312,96 +2537,96 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:77" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="68" t="s">
+    <row r="11" spans="1:78" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="72" t="s">
+      <c r="H11" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="61" t="s">
+      <c r="I11" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61" t="s">
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="61"/>
-      <c r="P11" s="62" t="s">
+      <c r="P11" s="87"/>
+      <c r="Q11" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="83" t="s">
+      <c r="R11" s="89"/>
+      <c r="S11" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="S11" s="84"/>
-      <c r="T11" s="61" t="s">
+      <c r="T11" s="70"/>
+      <c r="U11" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="U11" s="61"/>
-      <c r="V11" s="61"/>
-      <c r="W11" s="61"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="61"/>
-      <c r="Z11" s="61"/>
-      <c r="AA11" s="61"/>
-      <c r="AB11" s="61"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="61"/>
-      <c r="AE11" s="61"/>
-      <c r="AF11" s="61"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="68" t="s">
+      <c r="V11" s="102"/>
+      <c r="W11" s="102"/>
+      <c r="X11" s="102"/>
+      <c r="Y11" s="102"/>
+      <c r="Z11" s="102"/>
+      <c r="AA11" s="102"/>
+      <c r="AB11" s="102"/>
+      <c r="AC11" s="102"/>
+      <c r="AD11" s="102"/>
+      <c r="AE11" s="102"/>
+      <c r="AF11" s="102"/>
+      <c r="AG11" s="103"/>
+      <c r="AH11" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="AI11" s="89" t="s">
+      <c r="AI11" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="AJ11" s="89"/>
-      <c r="AK11" s="89"/>
-      <c r="AL11" s="89"/>
-      <c r="AM11" s="89"/>
-      <c r="AN11" s="89"/>
-      <c r="AO11" s="89"/>
-      <c r="AP11" s="90" t="s">
+      <c r="AJ11" s="77"/>
+      <c r="AK11" s="77"/>
+      <c r="AL11" s="77"/>
+      <c r="AM11" s="77"/>
+      <c r="AN11" s="77"/>
+      <c r="AO11" s="77"/>
+      <c r="AP11" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="AQ11" s="92" t="s">
+      <c r="AQ11" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="AR11" s="93"/>
-      <c r="AS11" s="93"/>
-      <c r="AT11" s="93"/>
-      <c r="AU11" s="93"/>
-      <c r="AV11" s="94" t="s">
+      <c r="AR11" s="81"/>
+      <c r="AS11" s="81"/>
+      <c r="AT11" s="81"/>
+      <c r="AU11" s="81"/>
+      <c r="AV11" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="AW11" s="96" t="s">
+      <c r="AW11" s="97" t="s">
         <v>16</v>
       </c>
       <c r="AX11" s="7"/>
-      <c r="AY11" s="85" t="s">
+      <c r="AY11" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AZ11" s="87" t="s">
+      <c r="AZ11" s="75" t="s">
         <v>18</v>
       </c>
       <c r="BA11" s="8"/>
@@ -2416,58 +2641,61 @@
       <c r="BG11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BH11" s="98" t="s">
+      <c r="BH11" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="BI11" s="74" t="s">
+      <c r="BI11" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="BJ11" s="74" t="s">
+      <c r="BJ11" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="BK11" s="76" t="s">
+      <c r="BK11" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="BL11" s="77"/>
-      <c r="BM11" s="78"/>
-      <c r="BN11" s="74" t="s">
+      <c r="BL11" s="66"/>
+      <c r="BM11" s="67"/>
+      <c r="BN11" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="BO11" s="79" t="s">
+      <c r="BO11" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="BP11" s="74" t="s">
+      <c r="BP11" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="BQ11" s="82" t="s">
+      <c r="BQ11" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="BR11" s="82"/>
-      <c r="BS11" s="79" t="s">
+      <c r="BR11" s="94"/>
+      <c r="BS11" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="BT11" s="79"/>
-      <c r="BU11" s="64" t="s">
+      <c r="BT11" s="68"/>
+      <c r="BU11" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="BV11" s="81" t="s">
+      <c r="BV11" s="93" t="s">
         <v>151</v>
       </c>
-      <c r="BW11" s="80" t="s">
+      <c r="BW11" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="BY11" s="80" t="s">
+      <c r="BY11" s="92" t="s">
         <v>90</v>
       </c>
+      <c r="BZ11" s="86" t="s">
+        <v>174</v>
+      </c>
     </row>
-    <row r="12" spans="1:77" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="67"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="73"/>
+    <row r="12" spans="1:78" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="83"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="48" t="s">
         <v>20</v>
       </c>
@@ -2480,44 +2708,44 @@
       <c r="L12" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="48" t="s">
+      <c r="M12" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="N12" s="41" t="s">
+      <c r="O12" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="O12" s="41" t="s">
+      <c r="P12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T12" s="41" t="s">
+      <c r="U12" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="U12" s="41" t="s">
+      <c r="V12" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="V12" s="42" t="s">
+      <c r="W12" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="W12" s="42" t="s">
+      <c r="X12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="X12" s="42" t="s">
+      <c r="Y12" s="42" t="s">
         <v>31</v>
-      </c>
-      <c r="Y12" s="42" t="s">
-        <v>32</v>
       </c>
       <c r="Z12" s="42" t="s">
         <v>33</v>
@@ -2543,7 +2771,7 @@
       <c r="AG12" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="AH12" s="69"/>
+      <c r="AH12" s="72"/>
       <c r="AI12" s="49">
         <v>1.5</v>
       </c>
@@ -2565,7 +2793,7 @@
       <c r="AO12" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AP12" s="91"/>
+      <c r="AP12" s="79"/>
       <c r="AQ12" s="46" t="s">
         <v>42</v>
       </c>
@@ -2581,11 +2809,11 @@
       <c r="AU12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="AV12" s="95"/>
-      <c r="AW12" s="97"/>
+      <c r="AV12" s="96"/>
+      <c r="AW12" s="98"/>
       <c r="AX12" s="9"/>
-      <c r="AY12" s="86"/>
-      <c r="AZ12" s="88"/>
+      <c r="AY12" s="74"/>
+      <c r="AZ12" s="76"/>
       <c r="BA12" s="10" t="str">
         <f>+IF(C12="SK2","SK2",IF(C12="FACTORY A","SK1 Box",IF(C12="FACTORY D","SK1 Bag","Chia")))</f>
         <v>Chia</v>
@@ -2595,9 +2823,9 @@
         <f>+IF(BA12="SK1 Box","Box",IF(BA12="Seaman","Seaman","Bag"))</f>
         <v>Bag</v>
       </c>
-      <c r="BH12" s="99"/>
-      <c r="BI12" s="75"/>
-      <c r="BJ12" s="75"/>
+      <c r="BH12" s="100"/>
+      <c r="BI12" s="64"/>
+      <c r="BJ12" s="64"/>
       <c r="BK12" s="35" t="s">
         <v>91</v>
       </c>
@@ -2607,9 +2835,9 @@
       <c r="BM12" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="BN12" s="75"/>
-      <c r="BO12" s="79"/>
-      <c r="BP12" s="75"/>
+      <c r="BN12" s="64"/>
+      <c r="BO12" s="68"/>
+      <c r="BP12" s="64"/>
       <c r="BQ12" s="34">
         <v>1</v>
       </c>
@@ -2622,15 +2850,16 @@
       <c r="BT12" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="BU12" s="64"/>
-      <c r="BV12" s="81"/>
-      <c r="BW12" s="80"/>
+      <c r="BU12" s="90"/>
+      <c r="BV12" s="93"/>
+      <c r="BW12" s="92"/>
       <c r="BX12" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BY12" s="80"/>
+      <c r="BY12" s="92"/>
+      <c r="BZ12" s="86"/>
     </row>
-    <row r="13" spans="1:77" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:78" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>1</v>
       </c>
@@ -2675,59 +2904,59 @@
         <v>11</v>
       </c>
       <c r="M13" s="44">
-        <f t="shared" si="0"/>
+        <f>Y13+1</f>
+        <v>24</v>
+      </c>
+      <c r="N13" s="44">
+        <f>L13+1</f>
         <v>12</v>
       </c>
-      <c r="N13" s="44">
+      <c r="O13" s="44">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="O13" s="44">
-        <f t="shared" ref="O13" si="1">N13+1</f>
+      <c r="P13" s="44">
+        <f t="shared" ref="P13" si="1">O13+1</f>
         <v>14</v>
       </c>
-      <c r="P13" s="6">
+      <c r="Q13" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="R13" s="6">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="R13" s="6">
+      <c r="S13" s="6">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="S13" s="6">
+      <c r="T13" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T13" s="44">
+      <c r="U13" s="44">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U13" s="44">
+      <c r="V13" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V13" s="44">
+      <c r="W13" s="44">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W13" s="44">
+      <c r="X13" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X13" s="44">
+      <c r="Y13" s="44">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y13" s="44">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
       <c r="Z13" s="44">
-        <f t="shared" si="0"/>
+        <f>M13+1</f>
         <v>25</v>
       </c>
       <c r="AA13" s="44">
@@ -2829,7 +3058,7 @@
       <c r="BB13" s="16"/>
       <c r="BC13" s="17"/>
     </row>
-    <row r="14" spans="1:77" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:78" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="18">
         <f>SUBTOTAL(3,C$14:C14)</f>
         <v>0</v>
@@ -2852,54 +3081,54 @@
       <c r="L14" s="22">
         <v>0</v>
       </c>
-      <c r="M14" s="23">
-        <f t="shared" ref="M14" si="4">SUM(I14:L14)</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="24">
+      <c r="M14" s="27">
+        <v>0</v>
+      </c>
+      <c r="N14" s="23">
+        <f>SUM(I14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="24">
         <f>ROUND((BQ14+BR14)/8,1)</f>
         <v>0</v>
       </c>
-      <c r="O14" s="50" t="e">
-        <f>ROUND(M14/IF($M$2&gt;26,26,BO14)*ROUND((BQ14+BR14)/8,1),0)</f>
+      <c r="P14" s="50" t="e">
+        <f>ROUND(N14/IF($N$2&gt;26,26,BO14)*ROUND((BQ14+BR14)/8,1),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P14" s="25">
+      <c r="Q14" s="25">
         <f>(BS14)/8</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="23" t="e">
-        <f>ROUND(M14/IF($M$2&gt;26,26,BO14)*ROUND(BS14/8,1),0)</f>
+      <c r="R14" s="23" t="e">
+        <f>ROUND(N14/IF($N$2&gt;26,26,BO14)*ROUND(BS14/8,1),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R14" s="26">
+      <c r="S14" s="26">
         <f>(BR14)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="23">
+      <c r="T14" s="23" t="e">
         <f>ROUND(BH14/8*BR14*0.3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T14" s="23" t="e">
-        <f>O14+Q14+S14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U14" s="40" t="e">
-        <f>BX14/BO14*ROUND((BQ14+BS14+BR14)/8,1)</f>
+      <c r="U14" s="23" t="e">
+        <f>P14+R14+T14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V14" s="51">
-        <v>0</v>
-      </c>
-      <c r="W14" s="28">
-        <v>0</v>
-      </c>
-      <c r="X14" s="27">
+      <c r="V14" s="40" t="e">
+        <f>ROUND(BX14/BO14*ROUND((BQ14+BS14+BR14)/8,1),0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14" s="51">
+        <v>0</v>
+      </c>
+      <c r="X14" s="28">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="27">
         <v>500000</v>
       </c>
-      <c r="Y14" s="27">
-        <v>0</v>
-      </c>
       <c r="Z14" s="27">
         <v>0</v>
       </c>
@@ -2919,14 +3148,14 @@
         <v>0</v>
       </c>
       <c r="AF14" s="23">
-        <f>IF(AND(BV14="Female",BQ14+BR14+BS14&gt;=13*8),1.5*BH14/8,0)</f>
+        <f>ROUND(IF(AND(BV14="Female",BQ14+BR14+BS14&gt;=13*8),1.5*BH14/8,0),0)</f>
         <v>0</v>
       </c>
       <c r="AG14" s="30">
         <v>0</v>
       </c>
       <c r="AH14" s="30" t="e">
-        <f t="shared" ref="AH14" si="5">ROUND(SUM(T14:AG14)-AB14,0)</f>
+        <f>ROUND(SUM(U14:AG14)-AB14,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI14" s="24">
@@ -2947,16 +3176,16 @@
       <c r="AN14" s="24">
         <v>0</v>
       </c>
-      <c r="AO14" s="50">
+      <c r="AO14" s="50" t="e">
         <f>ROUND(BH14/8*(AI14*1.5  + AJ14* 2  + AK14* 2.1  + AL14* 2.7  + AM14* 3 + AN14* 3.9),0)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AP14" s="31" t="e">
         <f>ROUND(AH14+AO14,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ14" s="50">
-        <f>IF(BP14=2,M14*4.5%,IF(BP14=1, M14*10.5%, 0))+BU14</f>
+        <f>ROUND(IF(BP14=2,N14*4.5%,IF(BP14=1, N14*10.5%, 0))+BU14,0)</f>
         <v>0</v>
       </c>
       <c r="AR14" s="23" t="e">
@@ -2964,7 +3193,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AS14" s="51" t="e">
-        <f>IF(BM14=1,IF(BJ14&gt;11000000,BJ14*10%,0),IF(BK14&gt;0,ROUND(IF(BK14&lt;5000000,BK14*0.05,IF(BK14&lt;10000000,BK14*0.1-250000,IF(BK14&lt;18000000,BK14*0.15-750000,IF(BK14&lt;32000000,BK14*0.2-1650000,IF(BK14&lt;52000000,BK14*0.25-3250000,IF(BK14&lt;80000000,BK14*0.3-5850000,BK14*0.35-9850000)))))),0),0))</f>
+        <f>ROUND(IF(BZ14&gt;0,BZ14,IF(BM14=1,IF(BJ14&gt;11000000,BJ14*10%,0),IF(BK14&lt;=0, 0, IF(BK14&lt;=10000000, BK14*5%, IF(BK14&lt;=30000000, BK14*10%-500000, IF(BK14&lt;=60000000, BK14*20%-3500000, IF(BK14&lt;=100000000, BK14*30%-9500000, BK14*35%-14500000))))))),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT14" s="23">
@@ -2974,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AV14" s="31" t="e">
-        <f t="shared" ref="AV14" si="6">+ROUND(SUM(AP14:AP14)-SUM(AQ14:AU14),0)</f>
+        <f t="shared" ref="AV14" si="4">+ROUND(SUM(AP14:AP14)-SUM(AQ14:AU14),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AW14" s="29"/>
@@ -3006,9 +3235,9 @@
         <f>$A$5</f>
         <v>5</v>
       </c>
-      <c r="BH14" s="4">
-        <f>IF(N14&gt;0,O14/IF(N14&gt;26,26,N14),0)</f>
-        <v>0</v>
+      <c r="BH14" s="4" t="e">
+        <f>N14/IF($N$2&gt;26,26,$N$2)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="BI14" s="4">
         <v>0</v>
@@ -3017,8 +3246,8 @@
         <f>AP14 + BN14 - AQ14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BK14" s="100" t="e">
-        <f>BJ14 -#REF! - U14 - BL14*4400000 - 11000000 - ROUND(BH14/8*(BR14*0.3 + AI14*0.5 + AJ14* 1 + AK14* 1.1 + AL14* 1.7 + AM14* 2 + AN14* 2.9),0)</f>
+      <c r="BK14" s="4" t="e">
+        <f>BJ14 - V14 - BL14*6200000 - 15500000 - ROUND(BH14/8*(BR14*0.3 + AI14*0.5 + AJ14* 1 + AK14* 1.1 + AL14* 1.7 + AM14* 2 + AN14* 2.9),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL14" s="4">
@@ -3056,14 +3285,42 @@
         <v>0</v>
       </c>
       <c r="BY14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ14" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A13:BC13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="34">
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:AG11"/>
+  <mergeCells count="35">
+    <mergeCell ref="BZ11:BZ12"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="BU11:BU12"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="BY11:BY12"/>
+    <mergeCell ref="BS11:BT11"/>
+    <mergeCell ref="BW11:BW12"/>
+    <mergeCell ref="BV11:BV12"/>
+    <mergeCell ref="BQ11:BR11"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="BH11:BH12"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="U11:AG11"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="BP11:BP12"/>
+    <mergeCell ref="BK11:BM11"/>
+    <mergeCell ref="BJ11:BJ12"/>
+    <mergeCell ref="BO11:BO12"/>
+    <mergeCell ref="S11:T11"/>
     <mergeCell ref="AH11:AH12"/>
     <mergeCell ref="AY11:AY12"/>
     <mergeCell ref="BN11:BN12"/>
@@ -3072,30 +3329,6 @@
     <mergeCell ref="AI11:AO11"/>
     <mergeCell ref="AP11:AP12"/>
     <mergeCell ref="AQ11:AU11"/>
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AW11:AW12"/>
-    <mergeCell ref="BH11:BH12"/>
-    <mergeCell ref="BY11:BY12"/>
-    <mergeCell ref="BS11:BT11"/>
-    <mergeCell ref="BW11:BW12"/>
-    <mergeCell ref="BV11:BV12"/>
-    <mergeCell ref="BQ11:BR11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="BU11:BU12"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BK11:BM11"/>
-    <mergeCell ref="BJ11:BJ12"/>
-    <mergeCell ref="BO11:BO12"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C11:C13 D13:AW13">
